--- a/fhir/StructureDefinition-ehealth-careplan.xlsx
+++ b/fhir/StructureDefinition-ehealth-careplan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -359,7 +359,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -821,7 +821,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -1011,7 +1011,7 @@
     <t>CarePlan.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
     <t>CarePlan.contributor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|RelatedPerson|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1303,7 +1303,7 @@
     <t>Identifies the results of the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
@@ -1361,7 +1361,7 @@
     <t>CarePlan.activity.progress.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1512,7 +1512,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1546,7 +1546,7 @@
     <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1573,7 +1573,7 @@
     <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1754,7 +1754,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|Substance)</t>
+Reference(Medication|4.0.1|Substance|4.0.1)</t>
   </si>
   <si>
     <t>What is to be administered/supplied</t>
@@ -1766,7 +1766,7 @@
     <t>A product supplied or administered as part of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=PRD].role</t>
@@ -1782,7 +1782,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -2187,7 +2187,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="136.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-careplan.xlsx
+++ b/fhir/StructureDefinition-ehealth-careplan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-careplan.xlsx
+++ b/fhir/StructureDefinition-ehealth-careplan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-careplan.xlsx
+++ b/fhir/StructureDefinition-ehealth-careplan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3771" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3771" uniqueCount="595">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -637,6 +637,12 @@
     <t>function</t>
   </si>
   <si>
+    <t>The function of the participant</t>
+  </si>
+  <si>
+    <t>The code defining the function of the participant.</t>
+  </si>
+  <si>
     <t>CarePlan.extension:participant.extension:function.id</t>
   </si>
   <si>
@@ -1793,6 +1799,10 @@
   </si>
   <si>
     <t>Allows rough dose checking.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP][classCode=SBADM].doseQuantity</t>
@@ -4622,10 +4632,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4705,10 +4715,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4817,10 +4827,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4929,10 +4939,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5043,10 +5053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5069,7 +5079,7 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>166</v>
@@ -5102,11 +5112,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -5153,13 +5163,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>153</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
@@ -5184,10 +5194,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5267,10 +5277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5379,10 +5389,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5491,10 +5501,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5534,7 +5544,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>78</v>
@@ -5605,10 +5615,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5631,7 +5641,7 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>166</v>
@@ -5717,13 +5727,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>153</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -5748,10 +5758,10 @@
         <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5831,10 +5841,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5943,10 +5953,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6055,10 +6065,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6098,7 +6108,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>78</v>
@@ -6169,10 +6179,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6281,7 +6291,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>157</v>
@@ -6324,7 +6334,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6395,7 +6405,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>164</v>
@@ -6421,7 +6431,7 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>166</v>
@@ -6507,10 +6517,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6536,16 +6546,16 @@
         <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>196</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6594,7 +6604,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6623,10 +6633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6649,19 +6659,19 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6710,7 +6720,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6725,24 +6735,24 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6765,13 +6775,13 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6822,7 +6832,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6837,10 +6847,10 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6851,10 +6861,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6880,13 +6890,13 @@
         <v>100</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6936,7 +6946,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6951,10 +6961,10 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6965,14 +6975,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6991,17 +7001,17 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7050,7 +7060,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7065,7 +7075,7 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
@@ -7079,14 +7089,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7105,19 +7115,19 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7166,7 +7176,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7181,7 +7191,7 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
@@ -7195,10 +7205,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7221,16 +7231,16 @@
         <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7280,7 +7290,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7309,10 +7319,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7338,16 +7348,16 @@
         <v>106</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7372,11 +7382,11 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7394,7 +7404,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>86</v>
@@ -7409,24 +7419,24 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7452,16 +7462,16 @@
         <v>106</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7486,13 +7496,13 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7510,7 +7520,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>86</v>
@@ -7525,7 +7535,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7539,10 +7549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7565,19 +7575,19 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7602,11 +7612,11 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7624,7 +7634,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7645,7 +7655,7 @@
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7653,10 +7663,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7682,10 +7692,10 @@
         <v>147</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7736,7 +7746,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7765,10 +7775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7794,14 +7804,14 @@
         <v>147</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7850,7 +7860,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7871,7 +7881,7 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7879,14 +7889,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7905,13 +7915,13 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7962,7 +7972,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>86</v>
@@ -7977,24 +7987,24 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8017,16 +8027,16 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8076,7 +8086,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8091,28 +8101,28 @@
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8131,19 +8141,19 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8192,7 +8202,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8207,28 +8217,28 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8247,13 +8257,13 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8304,7 +8314,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8319,13 +8329,13 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8333,10 +8343,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8359,16 +8369,16 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8418,7 +8428,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8433,13 +8443,13 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8447,10 +8457,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8473,16 +8483,16 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8532,7 +8542,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8561,10 +8571,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8587,17 +8597,17 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8646,7 +8656,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8661,13 +8671,13 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8675,10 +8685,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8701,19 +8711,19 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8762,7 +8772,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8777,24 +8787,24 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8817,19 +8827,19 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8878,7 +8888,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8893,7 +8903,7 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>78</v>
@@ -8907,10 +8917,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8933,19 +8943,19 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8994,7 +9004,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -9012,21 +9022,21 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9049,17 +9059,17 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9108,7 +9118,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9120,13 +9130,13 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9137,10 +9147,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9249,10 +9259,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9363,14 +9373,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9392,16 +9402,16 @@
         <v>131</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>196</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9450,7 +9460,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9479,10 +9489,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9505,16 +9515,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9540,13 +9550,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9564,7 +9574,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9593,10 +9603,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9619,19 +9629,19 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9680,7 +9690,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9695,10 +9705,10 @@
         <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9709,10 +9719,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9735,19 +9745,19 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9796,7 +9806,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9814,21 +9824,21 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9937,10 +9947,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10051,10 +10061,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10077,16 +10087,16 @@
         <v>87</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10124,17 +10134,17 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10152,7 +10162,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10163,13 +10173,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>78</v>
@@ -10191,16 +10201,16 @@
         <v>87</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10250,7 +10260,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10268,7 +10278,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10279,13 +10289,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
@@ -10310,13 +10320,13 @@
         <v>147</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10366,7 +10376,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10384,7 +10394,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10395,10 +10405,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10421,13 +10431,13 @@
         <v>87</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10478,7 +10488,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10496,7 +10506,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10507,10 +10517,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10533,13 +10543,13 @@
         <v>87</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10590,7 +10600,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>86</v>
@@ -10608,7 +10618,7 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10619,10 +10629,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10645,19 +10655,19 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10706,7 +10716,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10715,16 +10725,16 @@
         <v>86</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -10735,10 +10745,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10761,17 +10771,17 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10820,16 +10830,16 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI76" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>98</v>
@@ -10838,7 +10848,7 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10849,10 +10859,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10961,10 +10971,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11075,14 +11085,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11104,16 +11114,16 @@
         <v>131</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>196</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11162,7 +11172,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11191,10 +11201,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11220,14 +11230,14 @@
         <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11252,13 +11262,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11276,7 +11286,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11294,7 +11304,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11305,10 +11315,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11331,17 +11341,17 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11390,7 +11400,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11405,10 +11415,10 @@
         <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11419,10 +11429,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11448,16 +11458,16 @@
         <v>100</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M82" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O82" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11506,7 +11516,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11521,10 +11531,10 @@
         <v>98</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11535,10 +11545,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11561,19 +11571,19 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11598,13 +11608,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11622,7 +11632,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11637,24 +11647,24 @@
         <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11677,16 +11687,16 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11712,13 +11722,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11736,7 +11746,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11751,7 +11761,7 @@
         <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>78</v>
@@ -11765,10 +11775,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11791,16 +11801,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11850,7 +11860,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11865,7 +11875,7 @@
         <v>98</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>78</v>
@@ -11879,10 +11889,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11905,17 +11915,17 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -11964,7 +11974,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11982,7 +11992,7 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -11993,10 +12003,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12022,16 +12032,16 @@
         <v>106</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12056,13 +12066,13 @@
         <v>78</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -12080,7 +12090,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>86</v>
@@ -12095,24 +12105,24 @@
         <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12135,16 +12145,16 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12194,7 +12204,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12209,7 +12219,7 @@
         <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>78</v>
@@ -12223,10 +12233,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12249,70 +12259,70 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q89" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="R89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q89" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="R89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12327,10 +12337,10 @@
         <v>98</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12341,10 +12351,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12367,17 +12377,17 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12426,7 +12436,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12441,24 +12451,24 @@
         <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12481,19 +12491,19 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -12542,7 +12552,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12560,21 +12570,21 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12597,19 +12607,19 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -12658,7 +12668,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12673,24 +12683,24 @@
         <v>98</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12713,13 +12723,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12746,13 +12756,13 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12770,7 +12780,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12788,25 +12798,25 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12825,17 +12835,17 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -12884,7 +12894,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12896,27 +12906,27 @@
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>98</v>
+        <v>571</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12939,13 +12949,13 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12996,39 +13006,39 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AG95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13054,10 +13064,10 @@
         <v>147</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13108,7 +13118,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13126,21 +13136,21 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13163,17 +13173,17 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13222,7 +13232,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13237,24 +13247,24 @@
         <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13363,10 +13373,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13477,10 +13487,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13503,16 +13513,16 @@
         <v>87</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13550,17 +13560,17 @@
         <v>78</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AC100" s="2"/>
       <c r="AD100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13578,7 +13588,7 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13589,13 +13599,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>78</v>
@@ -13617,16 +13627,16 @@
         <v>87</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13676,7 +13686,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13694,7 +13704,7 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13705,13 +13715,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
@@ -13736,13 +13746,13 @@
         <v>147</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13792,7 +13802,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13810,7 +13820,7 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -13821,10 +13831,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13847,13 +13857,13 @@
         <v>87</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13904,7 +13914,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13922,7 +13932,7 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -13933,10 +13943,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13959,13 +13969,13 @@
         <v>87</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14016,7 +14026,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>86</v>
@@ -14034,7 +14044,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>

--- a/fhir/StructureDefinition-ehealth-careplan.xlsx
+++ b/fhir/StructureDefinition-ehealth-careplan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-careplan.xlsx
+++ b/fhir/StructureDefinition-ehealth-careplan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-careplan.xlsx
+++ b/fhir/StructureDefinition-ehealth-careplan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
